--- a/erp-server/erp-server-oms/src/main/resources/excel/skuMapingTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/skuMapingTemplate.xlsx
@@ -172,20 +172,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -492,39 +495,39 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="27.875" customWidth="1"/>
-    <col min="2" max="4" width="20.5" customWidth="1"/>
-    <col min="5" max="5" width="32.625" customWidth="1"/>
-    <col min="6" max="6" width="21.75" customWidth="1"/>
+    <col min="1" max="1" width="27.875" style="2" customWidth="1"/>
+    <col min="2" max="4" width="20.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="32.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="35.25" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="21" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/skuMapingTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/skuMapingTemplate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <r>
       <t>*</t>
@@ -101,10 +101,6 @@
   </si>
   <si>
     <t>平台产品名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -172,7 +168,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -183,9 +179,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -492,16 +485,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="27.875" style="2" customWidth="1"/>
     <col min="2" max="4" width="20.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="32.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="21.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="35.25" customHeight="1">
+    <row r="1" spans="1:5" ht="35.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -517,17 +509,13 @@
       <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="2" spans="1:6" ht="21" customHeight="1">
-      <c r="A2" s="5"/>
+    <row r="2" spans="1:5" ht="21" customHeight="1">
+      <c r="A2" s="4"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
